--- a/model/腿长拟合数据第二次.xlsx
+++ b/model/腿长拟合数据第二次.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\84103\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RM\Myself\BUAA_LegWheel-master\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF879026-04F2-4284-AD52-7DCAF035248E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53E60C4-2C80-4C81-8986-6327698D6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,6 +126,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN"/>
+              <a:t>腿部质心与轮毂中心距离拟合情况</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.0752688172043011E-3"/>
+          <c:y val="0"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -139,12 +169,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx2"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -164,6 +191,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>腿部质心与轮毂中心距离真实值</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
               <a:noFill/>
@@ -175,13 +205,329 @@
             <c:symbol val="circle"/>
             <c:size val="5"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
               <a:ln w="9525">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>9.3670000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9010000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10972</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.12012</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.13059999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13966000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.14906</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.159</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.17101</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.18078</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.19095999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.20047999999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.20943000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.22023000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.22927</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.24084</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.25037999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.26024000000000003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.26921</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.27983000000000002</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.28944999999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.3004</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.30909999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.31939000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.33056000000000002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.34045999999999998</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.34974</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.36098999999999998</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.36956</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>0.11990000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10508000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.8059999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.5619999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.5039999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.5449999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.647E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.8049999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.10047</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.10274999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.10536</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.10798000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.11057</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.11385000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.1167</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.12046999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.12368</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.12706999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.13020999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.13400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.13750000000000001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.14155999999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.14482999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.14874999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.15309</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.15695000000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.16070999999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.1653</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.16889000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-D12B-4526-9B44-A07244D91860}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>腿部质心与轮毂中心距离拟合值</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent2">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -284,96 +630,96 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$30</c:f>
+              <c:f>Sheet1!$E$2:$E$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>0.11990000000000001</c:v>
+                  <c:v>0.10155367396591</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.10508000000000001</c:v>
+                  <c:v>0.10128212477719001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.8059999999999994E-2</c:v>
+                  <c:v>0.10093550726896</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.5619999999999997E-2</c:v>
+                  <c:v>0.10085181530736001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.5039999999999999E-2</c:v>
+                  <c:v>0.10101954108400001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.5449999999999993E-2</c:v>
+                  <c:v>0.10136846427964</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.647E-2</c:v>
+                  <c:v>0.10193036401884001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.8049999999999998E-2</c:v>
+                  <c:v>0.1027459839</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.10047</c:v>
+                  <c:v>0.10403511951319</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.10274999999999999</c:v>
+                  <c:v>0.10532893033596</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.10536</c:v>
+                  <c:v>0.10691097671104</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.10798000000000001</c:v>
+                  <c:v>0.10860648619776</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.11057</c:v>
+                  <c:v>0.11039089539231001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.11385000000000001</c:v>
+                  <c:v>0.11278984921551001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1167</c:v>
+                  <c:v>0.11500445982751001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.12046999999999999</c:v>
+                  <c:v>0.11811354686064</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.12368</c:v>
+                  <c:v>0.12090911333436</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.12706999999999999</c:v>
+                  <c:v>0.12401879146944002</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.13020999999999999</c:v>
+                  <c:v>0.12704234036079001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.13400000000000001</c:v>
+                  <c:v>0.13086170840991002</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.13750000000000001</c:v>
+                  <c:v>0.13454572234974999</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.14155999999999999</c:v>
+                  <c:v>0.13899852030400001</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.14482999999999999</c:v>
+                  <c:v>0.142733282839</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.14874999999999999</c:v>
+                  <c:v>0.14737569486199004</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.15309</c:v>
+                  <c:v>0.15269124547584001</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.15695000000000001</c:v>
+                  <c:v>0.15764271006204</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.16070999999999999</c:v>
+                  <c:v>0.16248911006844</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1653</c:v>
+                  <c:v>0.16863037129719</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.16889000000000001</c:v>
+                  <c:v>0.17350430636784001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -381,554 +727,12 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4364-4C7F-800C-2A00368E96F6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
-                <c:pt idx="0">
-                  <c:v>9.3670000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9.9010000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.10972</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.12012</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.13059999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.13966000000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.14906</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.159</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.17101</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.18078</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.19095999999999999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.20047999999999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.20943000000000001</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.22023000000000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.22927</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.24084</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.25037999999999999</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.26024000000000003</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.26921</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.27983000000000002</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.28944999999999999</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.3004</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.30909999999999999</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.31939000000000001</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.33056000000000002</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.34045999999999998</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.34974</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.36098999999999998</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.36956</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$E$2:$E$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
-                <c:pt idx="0">
-                  <c:v>0.10155367396591</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.10128212477719001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.10093550726896</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.10085181530736001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.10101954108400001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.10136846427964</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.10193036401884001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.1027459839</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.10403511951319</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.10532893033596</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.10691097671104</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.10860648619776</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.11039089539231001</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.11278984921551001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.11500445982751001</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.11811354686064</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.12090911333436</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.12401879146944002</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.12704234036079001</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.13086170840991002</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.13454572234974999</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.13899852030400001</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.142733282839</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.14737569486199004</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.15269124547584001</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.15764271006204</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.16248911006844</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.16863037129719</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.17350430636784001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4364-4C7F-800C-2A00368E96F6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$A$2:$A$30</c:f>
-              <c:strCache>
-                <c:ptCount val="29"/>
-                <c:pt idx="0">
-                  <c:v>0.09367</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.09901</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.10972</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.12012</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1306</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.13966</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.14906</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.159</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.17101</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.18078</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.19096</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.20048</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.20943</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.22023</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.22927</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.24084</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.25038</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.26024</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.26921</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.27983</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.28945</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.3004</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.3091</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.31939</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.33056</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.34046</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.34974</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.36099</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.36956</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
-                <c:pt idx="0">
-                  <c:v>9.3670000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9.9010000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.10972</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.12012</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.13059999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.13966000000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.14906</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.159</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.17101</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.18078</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.19095999999999999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.20047999999999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.20943000000000001</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.22023000000000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.22927</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.24084</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.25037999999999999</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.26024000000000003</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.26921</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.27983000000000002</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.28944999999999999</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.3004</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.30909999999999999</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.31939000000000001</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.33056000000000002</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.34045999999999998</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.34974</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.36098999999999998</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.36956</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$F$2:$F$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
-                <c:pt idx="0">
-                  <c:v>9.808877686379E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9.8153270970109993E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.8440954454240004E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9.892253294384E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9.9609373195999995E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.10036621375915999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.10131128968396</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.10248772909999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.10415198135411</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.10570183327724</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.10750379216576</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.10936167142144</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.11126057592539</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.11374846204619</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.11599611747419</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.11909246144816001</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.12183104000684</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.12483767033536</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.12772848959851002</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.13134269589979003</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.13479592773275001</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.13893405137599998</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.14237934229099999</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.14663427930131001</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.15147389341696002</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.15595539098476</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.16032017606636001</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.16582427685011</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.17017363416496001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-4364-4C7F-800C-2A00368E96F6}"/>
+              <c16:uniqueId val="{00000004-D12B-4526-9B44-A07244D91860}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -950,7 +754,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="tx2">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
@@ -960,20 +764,73 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-CN"/>
+                  <a:t>虚拟腿长</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>/m</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-CN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln>
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -984,10 +841,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1012,7 +866,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="tx2">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
@@ -1022,20 +876,73 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-CN"/>
+                  <a:t>距离</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>/m</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-CN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln>
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1046,10 +953,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1071,6 +975,34 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -1088,7 +1020,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="tx2">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -1130,6 +1062,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>腿部转动惯量拟合情况</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1168,6 +1125,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>腿部转动惯量真实值</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
               <a:noFill/>
@@ -1190,6 +1150,51 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="4"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$A$2:$A$30</c:f>
@@ -1385,13 +1390,16 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9E1E-43B1-BC74-16E7A0A9E5C5}"/>
+              <c16:uniqueId val="{00000000-36EB-4EAA-8895-B34ED66E3D36}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>腿部转动惯量拟合值</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
               <a:noFill/>
@@ -1512,96 +1520,96 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$30</c:f>
+              <c:f>Sheet1!$F$2:$F$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>2.2963999502110002E-2</c:v>
+                  <c:v>2.1173020429774814E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3222303482990002E-2</c:v>
+                  <c:v>2.2058302842122401E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.3707685256160002E-2</c:v>
+                  <c:v>2.3528388633458568E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.4137282382560001E-2</c:v>
+                  <c:v>2.4611219390059308E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.4528585964E-2</c:v>
+                  <c:v>2.5409523363103849E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.4833215544440002E-2</c:v>
+                  <c:v>2.5898789312566575E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.511629022764E-2</c:v>
+                  <c:v>2.6241093489864573E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.5379081900000003E-2</c:v>
+                  <c:v>2.6451440114148003E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.5646485738990005E-2</c:v>
+                  <c:v>2.6541017050203633E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.5823564263160001E-2</c:v>
+                  <c:v>2.6512800851680535E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.596946632384E-2</c:v>
+                  <c:v>2.6413889066648377E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.6070257000960002E-2</c:v>
+                  <c:v>2.6277151432370624E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.6133588176510004E-2</c:v>
+                  <c:v>2.6124314829167813E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.6169461823710001E-2</c:v>
+                  <c:v>2.5924702709267139E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.6165394275710002E-2</c:v>
+                  <c:v>2.5755614925124237E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.6114857545440004E-2</c:v>
+                  <c:v>2.554818026047348E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.6034903549560003E-2</c:v>
+                  <c:v>2.5390892700145662E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.5915904570240005E-2</c:v>
+                  <c:v>2.524430014412718E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.5775538018590005E-2</c:v>
+                  <c:v>2.5124881755021922E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.5569802026110002E-2</c:v>
+                  <c:v>2.4997327826899896E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.5346424394750003E-2</c:v>
+                  <c:v>2.4888708739446902E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.5049345584000002E-2</c:v>
+                  <c:v>2.4761941146006217E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.4780811819000007E-2</c:v>
+                  <c:v>2.464828808558478E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.4426054303790003E-2</c:v>
+                  <c:v>2.4483698078332644E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.3995389424640003E-2</c:v>
+                  <c:v>2.4245116212340739E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2.3574036494840009E-2</c:v>
+                  <c:v>2.3957349897019725E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2.3145235349240005E-2</c:v>
+                  <c:v>2.3599645936768027E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2.2581500402990003E-2</c:v>
+                  <c:v>2.3018309234150963E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.2119769756639998E-2</c:v>
+                  <c:v>2.2440703809138124E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1609,231 +1617,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9E1E-43B1-BC74-16E7A0A9E5C5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
-                <c:pt idx="0">
-                  <c:v>9.3670000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9.9010000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.10972</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.12012</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.13059999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.13966000000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.14906</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.159</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.17101</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.18078</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.19095999999999999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.20047999999999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.20943000000000001</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.22023000000000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.22927</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.24084</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.25037999999999999</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.26024000000000003</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.26921</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.27983000000000002</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.28944999999999999</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.3004</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.30909999999999999</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.31939000000000001</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.33056000000000002</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.34045999999999998</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.34974</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.36098999999999998</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.36956</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$H$2:$H$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
-                <c:pt idx="0">
-                  <c:v>2.3202264287E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.3437461382999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.3879954671999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.4272317552000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.4630498800000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.4910052347999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.5170597788000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.5413430000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2.5662016582999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2.5828064572000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.5966555328000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2.6064184832000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.6127866766999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2.6168451007E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2.6171931406999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2.6135848048000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2.6071859451999996E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2.5973206207999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2.5854743903000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2.5679123087000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2.5486938575E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2.5229892800000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2.4996602299999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2.4687456742999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2.4311122687999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2.3942116027999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2.3565960508E-2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2.3070689382999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>2.2664527088E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-9E1E-43B1-BC74-16E7A0A9E5C5}"/>
+              <c16:uniqueId val="{00000003-36EB-4EAA-8895-B34ED66E3D36}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1845,11 +1629,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="2139828480"/>
-        <c:axId val="2139825120"/>
+        <c:axId val="1901843135"/>
+        <c:axId val="1901838815"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="2139828480"/>
+        <c:axId val="1901843135"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1869,6 +1653,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-CN" altLang="en-US"/>
+                  <a:t>虚拟腿长</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-CN"/>
+                  <a:t>/m</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-CN" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-CN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1906,12 +1750,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2139825120"/>
+        <c:crossAx val="1901838815"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2139825120"/>
+        <c:axId val="1901838815"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1931,6 +1775,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-CN" altLang="en-US"/>
+                  <a:t>转动惯量</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-CN"/>
+                  <a:t>/N*m</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-CN" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-CN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1968,7 +1872,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2139828480"/>
+        <c:crossAx val="1901843135"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1980,6 +1884,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -2105,35 +2040,29 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2146,7 +2075,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -2154,7 +2083,7 @@
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -2162,17 +2091,14 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
@@ -2181,9 +2107,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
@@ -2206,6 +2131,495 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
     <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
@@ -2620,536 +3034,20 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>44450</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>654050</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3176,23 +3074,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>501650</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="图表 2">
+        <xdr:cNvPr id="4" name="图表 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F8B25E2-FCC2-9E74-145C-E061D6A86E59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05F57DC2-3746-8C15-6185-343096D64ADA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3476,7 +3374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.4140625" customWidth="1"/>
@@ -3484,7 +3382,7 @@
     <col min="4" max="4" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3498,7 +3396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>9.3670000000000003E-2</v>
       </c>
@@ -3516,19 +3414,11 @@
         <v>0.10155367396591</v>
       </c>
       <c r="F2">
-        <f>0.9211*A2*A2-0.1654*A2+0.1055</f>
-        <v>9.808877686379E-2</v>
-      </c>
-      <c r="G2">
-        <f>-0.1901*A2*A2+0.085*A2+0.01667</f>
-        <v>2.2963999502110002E-2</v>
-      </c>
-      <c r="H2">
-        <f>-0.17*A2*A2+0.0768*A2+0.0175</f>
-        <v>2.3202264287E-2</v>
+        <f>-13.132*A2^4+13.37*A2^3-5.0186*A2^2+0.8074*A2-0.0204</f>
+        <v>2.1173020429774814E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>9.9010000000000001E-2</v>
       </c>
@@ -3546,19 +3436,11 @@
         <v>0.10128212477719001</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F30" si="1">0.9211*A3*A3-0.1654*A3+0.1055</f>
-        <v>9.8153270970109993E-2</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G30" si="2">-0.1901*A3*A3+0.085*A3+0.01667</f>
-        <v>2.3222303482990002E-2</v>
-      </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H30" si="3">-0.17*A3*A3+0.0768*A3+0.0175</f>
-        <v>2.3437461382999999E-2</v>
+        <f t="shared" ref="F3:F30" si="1">-13.132*A3^4+13.37*A3^3-5.0186*A3^2+0.8074*A3-0.0204</f>
+        <v>2.2058302842122401E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.10972</v>
       </c>
@@ -3577,18 +3459,10 @@
       </c>
       <c r="F4">
         <f t="shared" si="1"/>
-        <v>9.8440954454240004E-2</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="2"/>
-        <v>2.3707685256160002E-2</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="3"/>
-        <v>2.3879954671999999E-2</v>
+        <v>2.3528388633458568E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.12012</v>
       </c>
@@ -3607,18 +3481,10 @@
       </c>
       <c r="F5">
         <f t="shared" si="1"/>
-        <v>9.892253294384E-2</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="2"/>
-        <v>2.4137282382560001E-2</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="3"/>
-        <v>2.4272317552000003E-2</v>
+        <v>2.4611219390059308E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.13059999999999999</v>
       </c>
@@ -3637,18 +3503,10 @@
       </c>
       <c r="F6">
         <f t="shared" si="1"/>
-        <v>9.9609373195999995E-2</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="2"/>
-        <v>2.4528585964E-2</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="3"/>
-        <v>2.4630498800000001E-2</v>
+        <v>2.5409523363103849E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.13966000000000001</v>
       </c>
@@ -3667,18 +3525,10 @@
       </c>
       <c r="F7">
         <f t="shared" si="1"/>
-        <v>0.10036621375915999</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="2"/>
-        <v>2.4833215544440002E-2</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="3"/>
-        <v>2.4910052347999999E-2</v>
+        <v>2.5898789312566575E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.14906</v>
       </c>
@@ -3697,18 +3547,10 @@
       </c>
       <c r="F8">
         <f t="shared" si="1"/>
-        <v>0.10131128968396</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="2"/>
-        <v>2.511629022764E-2</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="3"/>
-        <v>2.5170597788000001E-2</v>
+        <v>2.6241093489864573E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.159</v>
       </c>
@@ -3727,18 +3569,10 @@
       </c>
       <c r="F9">
         <f t="shared" si="1"/>
-        <v>0.10248772909999999</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="2"/>
-        <v>2.5379081900000003E-2</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="3"/>
-        <v>2.5413430000000001E-2</v>
+        <v>2.6451440114148003E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.17101</v>
       </c>
@@ -3757,18 +3591,10 @@
       </c>
       <c r="F10">
         <f t="shared" si="1"/>
-        <v>0.10415198135411</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="2"/>
-        <v>2.5646485738990005E-2</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="3"/>
-        <v>2.5662016582999998E-2</v>
+        <v>2.6541017050203633E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.18078</v>
       </c>
@@ -3787,18 +3613,10 @@
       </c>
       <c r="F11">
         <f t="shared" si="1"/>
-        <v>0.10570183327724</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="2"/>
-        <v>2.5823564263160001E-2</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="3"/>
-        <v>2.5828064572000001E-2</v>
+        <v>2.6512800851680535E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.19095999999999999</v>
       </c>
@@ -3817,18 +3635,10 @@
       </c>
       <c r="F12">
         <f t="shared" si="1"/>
-        <v>0.10750379216576</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="2"/>
-        <v>2.596946632384E-2</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="3"/>
-        <v>2.5966555328000001E-2</v>
+        <v>2.6413889066648377E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.20047999999999999</v>
       </c>
@@ -3847,18 +3657,10 @@
       </c>
       <c r="F13">
         <f t="shared" si="1"/>
-        <v>0.10936167142144</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="2"/>
-        <v>2.6070257000960002E-2</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="3"/>
-        <v>2.6064184832000001E-2</v>
+        <v>2.6277151432370624E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.20943000000000001</v>
       </c>
@@ -3877,18 +3679,10 @@
       </c>
       <c r="F14">
         <f t="shared" si="1"/>
-        <v>0.11126057592539</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="2"/>
-        <v>2.6133588176510004E-2</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="3"/>
-        <v>2.6127866766999998E-2</v>
+        <v>2.6124314829167813E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.22023000000000001</v>
       </c>
@@ -3907,18 +3701,10 @@
       </c>
       <c r="F15">
         <f t="shared" si="1"/>
-        <v>0.11374846204619</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="2"/>
-        <v>2.6169461823710001E-2</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="3"/>
-        <v>2.6168451007E-2</v>
+        <v>2.5924702709267139E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.22927</v>
       </c>
@@ -3937,18 +3723,10 @@
       </c>
       <c r="F16">
         <f t="shared" si="1"/>
-        <v>0.11599611747419</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="2"/>
-        <v>2.6165394275710002E-2</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="3"/>
-        <v>2.6171931406999999E-2</v>
+        <v>2.5755614925124237E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.24084</v>
       </c>
@@ -3967,18 +3745,10 @@
       </c>
       <c r="F17">
         <f t="shared" si="1"/>
-        <v>0.11909246144816001</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="2"/>
-        <v>2.6114857545440004E-2</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="3"/>
-        <v>2.6135848048000003E-2</v>
+        <v>2.554818026047348E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.25037999999999999</v>
       </c>
@@ -3997,18 +3767,10 @@
       </c>
       <c r="F18">
         <f t="shared" si="1"/>
-        <v>0.12183104000684</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="2"/>
-        <v>2.6034903549560003E-2</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="3"/>
-        <v>2.6071859451999996E-2</v>
+        <v>2.5390892700145662E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.26024000000000003</v>
       </c>
@@ -4027,18 +3789,10 @@
       </c>
       <c r="F19">
         <f t="shared" si="1"/>
-        <v>0.12483767033536</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="2"/>
-        <v>2.5915904570240005E-2</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="3"/>
-        <v>2.5973206207999998E-2</v>
+        <v>2.524430014412718E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.26921</v>
       </c>
@@ -4057,18 +3811,10 @@
       </c>
       <c r="F20">
         <f t="shared" si="1"/>
-        <v>0.12772848959851002</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="2"/>
-        <v>2.5775538018590005E-2</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="3"/>
-        <v>2.5854743903000001E-2</v>
+        <v>2.5124881755021922E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.27983000000000002</v>
       </c>
@@ -4087,18 +3833,10 @@
       </c>
       <c r="F21">
         <f t="shared" si="1"/>
-        <v>0.13134269589979003</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="2"/>
-        <v>2.5569802026110002E-2</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="3"/>
-        <v>2.5679123087000003E-2</v>
+        <v>2.4997327826899896E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0.28944999999999999</v>
       </c>
@@ -4117,18 +3855,10 @@
       </c>
       <c r="F22">
         <f t="shared" si="1"/>
-        <v>0.13479592773275001</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="2"/>
-        <v>2.5346424394750003E-2</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="3"/>
-        <v>2.5486938575E-2</v>
+        <v>2.4888708739446902E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.3004</v>
       </c>
@@ -4147,18 +3877,10 @@
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
-        <v>0.13893405137599998</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="2"/>
-        <v>2.5049345584000002E-2</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="3"/>
-        <v>2.5229892800000001E-2</v>
+        <v>2.4761941146006217E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.30909999999999999</v>
       </c>
@@ -4177,18 +3899,10 @@
       </c>
       <c r="F24">
         <f t="shared" si="1"/>
-        <v>0.14237934229099999</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="2"/>
-        <v>2.4780811819000007E-2</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="3"/>
-        <v>2.4996602299999997E-2</v>
+        <v>2.464828808558478E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.31939000000000001</v>
       </c>
@@ -4207,18 +3921,10 @@
       </c>
       <c r="F25">
         <f t="shared" si="1"/>
-        <v>0.14663427930131001</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="2"/>
-        <v>2.4426054303790003E-2</v>
-      </c>
-      <c r="H25">
-        <f t="shared" si="3"/>
-        <v>2.4687456742999998E-2</v>
+        <v>2.4483698078332644E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.33056000000000002</v>
       </c>
@@ -4237,18 +3943,10 @@
       </c>
       <c r="F26">
         <f t="shared" si="1"/>
-        <v>0.15147389341696002</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="2"/>
-        <v>2.3995389424640003E-2</v>
-      </c>
-      <c r="H26">
-        <f t="shared" si="3"/>
-        <v>2.4311122687999998E-2</v>
+        <v>2.4245116212340739E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.34045999999999998</v>
       </c>
@@ -4267,18 +3965,10 @@
       </c>
       <c r="F27">
         <f t="shared" si="1"/>
-        <v>0.15595539098476</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="2"/>
-        <v>2.3574036494840009E-2</v>
-      </c>
-      <c r="H27">
-        <f t="shared" si="3"/>
-        <v>2.3942116027999998E-2</v>
+        <v>2.3957349897019725E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.34974</v>
       </c>
@@ -4297,18 +3987,10 @@
       </c>
       <c r="F28">
         <f t="shared" si="1"/>
-        <v>0.16032017606636001</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="2"/>
-        <v>2.3145235349240005E-2</v>
-      </c>
-      <c r="H28">
-        <f t="shared" si="3"/>
-        <v>2.3565960508E-2</v>
+        <v>2.3599645936768027E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.36098999999999998</v>
       </c>
@@ -4327,18 +4009,10 @@
       </c>
       <c r="F29">
         <f t="shared" si="1"/>
-        <v>0.16582427685011</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="2"/>
-        <v>2.2581500402990003E-2</v>
-      </c>
-      <c r="H29">
-        <f t="shared" si="3"/>
-        <v>2.3070689382999998E-2</v>
+        <v>2.3018309234150963E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.36956</v>
       </c>
@@ -4357,15 +4031,7 @@
       </c>
       <c r="F30">
         <f t="shared" si="1"/>
-        <v>0.17017363416496001</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="2"/>
-        <v>2.2119769756639998E-2</v>
-      </c>
-      <c r="H30">
-        <f t="shared" si="3"/>
-        <v>2.2664527088E-2</v>
+        <v>2.2440703809138124E-2</v>
       </c>
     </row>
   </sheetData>
